--- a/Results_experiment/exp_1/preds_1111122222222222.xlsx
+++ b/Results_experiment/exp_1/preds_1111122222222222.xlsx
@@ -1629,7 +1629,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D2">
-        <v>-0.8522385358810425</v>
+        <v>0.5287631154060364</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1643,7 +1643,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D3">
-        <v>0.986022412776947</v>
+        <v>1.069087743759155</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1657,7 +1657,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D4">
-        <v>-2.037286281585693</v>
+        <v>-2.189505100250244</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1671,7 +1671,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D5">
-        <v>1.250394821166992</v>
+        <v>-3.768611669540405</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1685,7 +1685,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D6">
-        <v>-13.54241180419922</v>
+        <v>-11.60498809814453</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1699,7 +1699,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D7">
-        <v>-7.970332145690918</v>
+        <v>-7.312862873077393</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1713,7 +1713,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D8">
-        <v>-10.24226093292236</v>
+        <v>-7.950529098510742</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1727,7 +1727,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D9">
-        <v>1.188808679580688</v>
+        <v>0.5604613423347473</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1741,7 +1741,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D10">
-        <v>-9.847329139709473</v>
+        <v>-8.060376167297363</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1755,7 +1755,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D11">
-        <v>1.71740460395813</v>
+        <v>0.9109421372413635</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1769,7 +1769,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D12">
-        <v>5.920229434967041</v>
+        <v>6.011705875396729</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1783,7 +1783,7 @@
         <v>-0.5</v>
       </c>
       <c r="D13">
-        <v>1.469179511070251</v>
+        <v>0.8940332531929016</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1797,7 +1797,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D14">
-        <v>-0.2579618692398071</v>
+        <v>-0.09509736299514771</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1811,7 +1811,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D15">
-        <v>-6.562095642089844</v>
+        <v>-8.023434638977051</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1825,7 +1825,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D16">
-        <v>-1.998070478439331</v>
+        <v>-1.76185941696167</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1839,7 +1839,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D17">
-        <v>3.241779327392578</v>
+        <v>2.677318572998047</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1853,7 +1853,7 @@
         <v>-10.5</v>
       </c>
       <c r="D18">
-        <v>-7.804111480712891</v>
+        <v>-8.653362274169922</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1867,7 +1867,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D19">
-        <v>-4.241532325744629</v>
+        <v>-4.432301998138428</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1881,7 +1881,7 @@
         <v>-23</v>
       </c>
       <c r="D20">
-        <v>-19.6597843170166</v>
+        <v>-19.26925659179688</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1895,7 +1895,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D21">
-        <v>-1.392092704772949</v>
+        <v>-2.510623216629028</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1909,7 +1909,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D22">
-        <v>-5.808555603027344</v>
+        <v>-6.841923236846924</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1923,7 +1923,7 @@
         <v>-22</v>
       </c>
       <c r="D23">
-        <v>-14.88370990753174</v>
+        <v>-13.31830883026123</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1937,7 +1937,7 @@
         <v>-9.5</v>
       </c>
       <c r="D24">
-        <v>-7.87498140335083</v>
+        <v>-5.776388645172119</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1951,7 +1951,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D25">
-        <v>-0.9923077821731567</v>
+        <v>-1.869788408279419</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1965,7 +1965,7 @@
         <v>-22.20000076293945</v>
       </c>
       <c r="D26">
-        <v>-17.34325981140137</v>
+        <v>-15.88986396789551</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1979,7 +1979,7 @@
         <v>6.5</v>
       </c>
       <c r="D27">
-        <v>2.068092107772827</v>
+        <v>0.7658179402351379</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1993,7 +1993,7 @@
         <v>-20.29999923706055</v>
       </c>
       <c r="D28">
-        <v>-11.4685697555542</v>
+        <v>-11.10883140563965</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2007,7 +2007,7 @@
         <v>-15.19999980926514</v>
       </c>
       <c r="D29">
-        <v>-10.79861545562744</v>
+        <v>-8.324394226074219</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2021,7 +2021,7 @@
         <v>-2</v>
       </c>
       <c r="D30">
-        <v>-7.65794849395752</v>
+        <v>-5.584555149078369</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2035,7 +2035,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D31">
-        <v>-6.500212669372559</v>
+        <v>-10.39009284973145</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2049,7 +2049,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D32">
-        <v>-11.39856433868408</v>
+        <v>-10.87409687042236</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2063,7 +2063,7 @@
         <v>26.39999961853027</v>
       </c>
       <c r="D33">
-        <v>17.32296180725098</v>
+        <v>15.50244140625</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2077,7 +2077,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D34">
-        <v>5.676973342895508</v>
+        <v>4.645324230194092</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2091,7 +2091,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>1.452828407287598</v>
+        <v>1.017234563827515</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>4.040875911712646</v>
+        <v>2.340211391448975</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2119,7 +2119,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D37">
-        <v>2.14219069480896</v>
+        <v>1.743257999420166</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2133,7 +2133,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D38">
-        <v>-5.314866065979004</v>
+        <v>-5.105427742004395</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2147,7 +2147,7 @@
         <v>26.5</v>
       </c>
       <c r="D39">
-        <v>16.66033935546875</v>
+        <v>16.52111434936523</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2161,7 +2161,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D40">
-        <v>-3.073251008987427</v>
+        <v>-1.802395582199097</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>0.3454673886299133</v>
+        <v>-0.7563384771347046</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2189,7 +2189,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D42">
-        <v>2.349072456359863</v>
+        <v>1.473078489303589</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2203,7 +2203,7 @@
         <v>-16.70000076293945</v>
       </c>
       <c r="D43">
-        <v>-14.65431594848633</v>
+        <v>-13.63711929321289</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2217,7 +2217,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D44">
-        <v>-6.984210014343262</v>
+        <v>-6.895494937896729</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2231,7 +2231,7 @@
         <v>-0.5</v>
       </c>
       <c r="D45">
-        <v>-0.6386330723762512</v>
+        <v>-0.3706583082675934</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2245,7 +2245,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>0.972639262676239</v>
+        <v>-2.574069738388062</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2259,7 +2259,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D47">
-        <v>2.125632524490356</v>
+        <v>2.727815628051758</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2273,7 +2273,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D48">
-        <v>-1.899630784988403</v>
+        <v>-3.437402486801147</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2287,7 +2287,7 @@
         <v>-9</v>
       </c>
       <c r="D49">
-        <v>-6.912693023681641</v>
+        <v>-8.872739791870117</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2301,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>1.028770923614502</v>
+        <v>-0.2376608848571777</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2315,7 +2315,7 @@
         <v>-7</v>
       </c>
       <c r="D51">
-        <v>-3.352904558181763</v>
+        <v>-3.17740535736084</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2329,7 +2329,7 @@
         <v>-4</v>
       </c>
       <c r="D52">
-        <v>-2.29297661781311</v>
+        <v>-3.334141731262207</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2343,7 +2343,7 @@
         <v>4.5</v>
       </c>
       <c r="D53">
-        <v>1.61699914932251</v>
+        <v>0.7579987645149231</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2357,7 +2357,7 @@
         <v>0.5</v>
       </c>
       <c r="D54">
-        <v>-0.3581613898277283</v>
+        <v>0.4753339886665344</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2371,7 +2371,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D55">
-        <v>5.19333553314209</v>
+        <v>4.374009609222412</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2385,7 +2385,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D56">
-        <v>4.879271507263184</v>
+        <v>4.354191303253174</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2399,7 +2399,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D57">
-        <v>-22.32992172241211</v>
+        <v>-18.42754173278809</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2413,7 +2413,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D58">
-        <v>-5.919187545776367</v>
+        <v>-4.008977890014648</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2427,7 +2427,7 @@
         <v>-24.20000076293945</v>
       </c>
       <c r="D59">
-        <v>-12.96351146697998</v>
+        <v>-12.82551193237305</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2441,7 +2441,7 @@
         <v>-24.39999961853027</v>
       </c>
       <c r="D60">
-        <v>-16.39436531066895</v>
+        <v>-16.40816688537598</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2455,7 +2455,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D61">
-        <v>2.596712350845337</v>
+        <v>2.192405223846436</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2469,7 +2469,7 @@
         <v>0.5</v>
       </c>
       <c r="D62">
-        <v>-1.536893129348755</v>
+        <v>-0.8792427778244019</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2483,7 +2483,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D63">
-        <v>-11.37868118286133</v>
+        <v>-6.800725936889648</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2497,7 +2497,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D64">
-        <v>-3.117765188217163</v>
+        <v>-2.384309768676758</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2511,7 +2511,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D65">
-        <v>2.656755685806274</v>
+        <v>2.8360915184021</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2525,7 +2525,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D66">
-        <v>-5.43803596496582</v>
+        <v>-2.642826318740845</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2539,7 +2539,7 @@
         <v>-1</v>
       </c>
       <c r="D67">
-        <v>-0.7478675246238708</v>
+        <v>-0.2364644706249237</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2553,7 +2553,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D68">
-        <v>-4.638620376586914</v>
+        <v>-5.27251672744751</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2567,7 +2567,7 @@
         <v>-4.5</v>
       </c>
       <c r="D69">
-        <v>-2.655342578887939</v>
+        <v>-4.706477642059326</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2581,7 +2581,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D70">
-        <v>-3.301833629608154</v>
+        <v>-4.015395164489746</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2595,7 +2595,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D71">
-        <v>1.463257193565369</v>
+        <v>-0.4142239391803741</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2609,7 +2609,7 @@
         <v>-15</v>
       </c>
       <c r="D72">
-        <v>-12.10680866241455</v>
+        <v>-13.0860652923584</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2623,7 +2623,7 @@
         <v>8.5</v>
       </c>
       <c r="D73">
-        <v>9.238476753234863</v>
+        <v>10.06038665771484</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2637,7 +2637,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D74">
-        <v>-1.369824051856995</v>
+        <v>-0.8435261845588684</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2651,7 +2651,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D75">
-        <v>11.80211067199707</v>
+        <v>9.73582935333252</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2665,7 +2665,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D76">
-        <v>-1.96068549156189</v>
+        <v>1.145732879638672</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2679,7 +2679,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D77">
-        <v>-3.417380332946777</v>
+        <v>-2.670601844787598</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2693,7 +2693,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D78">
-        <v>-3.371209144592285</v>
+        <v>-2.701074600219727</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2707,7 +2707,7 @@
         <v>-1</v>
       </c>
       <c r="D79">
-        <v>-0.4431236386299133</v>
+        <v>-0.432752937078476</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2721,7 +2721,7 @@
         <v>-8.5</v>
       </c>
       <c r="D80">
-        <v>-0.6529167890548706</v>
+        <v>-3.452371120452881</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2735,7 +2735,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D81">
-        <v>-5.680982112884521</v>
+        <v>-4.1291184425354</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="D82">
-        <v>4.631022453308105</v>
+        <v>3.485905170440674</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2763,7 +2763,7 @@
         <v>-34.79999923706055</v>
       </c>
       <c r="D83">
-        <v>-15.23609924316406</v>
+        <v>-12.75583839416504</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2777,7 +2777,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D84">
-        <v>-2.795435190200806</v>
+        <v>-2.926358461380005</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2791,7 +2791,7 @@
         <v>-29</v>
       </c>
       <c r="D85">
-        <v>-6.217529296875</v>
+        <v>-5.03432035446167</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2805,7 +2805,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D86">
-        <v>-7.398268699645996</v>
+        <v>-5.228945732116699</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2819,7 +2819,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D87">
-        <v>-1.430101156234741</v>
+        <v>-2.108056545257568</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2833,7 +2833,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D88">
-        <v>7.184690475463867</v>
+        <v>7.644802570343018</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2847,7 +2847,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D89">
-        <v>-13.80745601654053</v>
+        <v>-12.05866432189941</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2861,7 +2861,7 @@
         <v>-9</v>
       </c>
       <c r="D90">
-        <v>-4.703486919403076</v>
+        <v>-7.501114368438721</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2875,7 +2875,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D91">
-        <v>6.380825042724609</v>
+        <v>7.648148059844971</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2889,7 +2889,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D92">
-        <v>2.953406810760498</v>
+        <v>1.830434322357178</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2903,7 +2903,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D93">
-        <v>4.557588577270508</v>
+        <v>3.853365421295166</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2917,7 +2917,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D94">
-        <v>-1.051019430160522</v>
+        <v>-0.5832451581954956</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2931,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>0.812048614025116</v>
+        <v>-1.880392551422119</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2945,7 +2945,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D96">
-        <v>-1.175363421440125</v>
+        <v>0.6228590607643127</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2959,7 +2959,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D97">
-        <v>-0.03018154203891754</v>
+        <v>0.2953154444694519</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2973,7 +2973,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D98">
-        <v>3.117289304733276</v>
+        <v>0.3933680653572083</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2987,7 +2987,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D99">
-        <v>0.1020316034555435</v>
+        <v>-0.1791200041770935</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3001,7 +3001,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D100">
-        <v>0.9783452153205872</v>
+        <v>1.641713380813599</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="D101">
-        <v>-3.42920708656311</v>
+        <v>-3.399353981018066</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3029,7 +3029,7 @@
         <v>5.5</v>
       </c>
       <c r="D102">
-        <v>1.791763544082642</v>
+        <v>1.665036916732788</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3043,7 +3043,7 @@
         <v>19.5</v>
       </c>
       <c r="D103">
-        <v>4.827110290527344</v>
+        <v>4.443504810333252</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3057,7 +3057,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D104">
-        <v>2.301513433456421</v>
+        <v>2.090237617492676</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3071,7 +3071,7 @@
         <v>-21.5</v>
       </c>
       <c r="D105">
-        <v>-12.98819065093994</v>
+        <v>-12.9623384475708</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3085,7 +3085,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D106">
-        <v>-3.666519641876221</v>
+        <v>-1.417976856231689</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3099,7 +3099,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D107">
-        <v>5.580330848693848</v>
+        <v>4.630989074707031</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3113,7 +3113,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D108">
-        <v>-3.170975923538208</v>
+        <v>-2.237664699554443</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3127,7 +3127,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D109">
-        <v>1.322046637535095</v>
+        <v>1.198221445083618</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3141,7 +3141,7 @@
         <v>10.5</v>
       </c>
       <c r="D110">
-        <v>5.232167720794678</v>
+        <v>4.015938282012939</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3155,7 +3155,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D111">
-        <v>1.969627618789673</v>
+        <v>0.987509548664093</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3169,7 +3169,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D112">
-        <v>-0.7183299660682678</v>
+        <v>0.9766187071800232</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3183,7 +3183,7 @@
         <v>-18.5</v>
       </c>
       <c r="D113">
-        <v>-10.00543975830078</v>
+        <v>-10.36066818237305</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3197,7 +3197,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D114">
-        <v>-21.0144214630127</v>
+        <v>-21.89462089538574</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3211,7 +3211,7 @@
         <v>-32.09999847412109</v>
       </c>
       <c r="D115">
-        <v>-15.66910076141357</v>
+        <v>-14.92857360839844</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3225,7 +3225,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D116">
-        <v>-2.212348461151123</v>
+        <v>-2.785478115081787</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3239,7 +3239,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D117">
-        <v>5.457286357879639</v>
+        <v>6.153333187103271</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3253,7 +3253,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D118">
-        <v>1.188533782958984</v>
+        <v>-0.05639022588729858</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3267,7 +3267,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D119">
-        <v>-0.02610348165035248</v>
+        <v>-0.04740989208221436</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3281,7 +3281,7 @@
         <v>43.59999847412109</v>
       </c>
       <c r="D120">
-        <v>23.08710861206055</v>
+        <v>23.66654777526855</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3295,7 +3295,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D121">
-        <v>-25.43534278869629</v>
+        <v>-22.40445137023926</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3309,7 +3309,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D122">
-        <v>1.055725574493408</v>
+        <v>0.1402900815010071</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3323,7 +3323,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D123">
-        <v>-7.433710098266602</v>
+        <v>-4.803397655487061</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>2.601415872573853</v>
+        <v>1.567494869232178</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3351,7 +3351,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D125">
-        <v>-2.048478603363037</v>
+        <v>-0.2418120503425598</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3365,7 +3365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D126">
-        <v>7.691939353942871</v>
+        <v>7.459851741790771</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3379,7 +3379,7 @@
         <v>-17.10000038146973</v>
       </c>
       <c r="D127">
-        <v>-7.831578254699707</v>
+        <v>-2.997137069702148</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3393,7 +3393,7 @@
         <v>-8</v>
       </c>
       <c r="D128">
-        <v>-6.936976909637451</v>
+        <v>-4.163305759429932</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3407,7 +3407,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D129">
-        <v>-1.905118346214294</v>
+        <v>-3.690206050872803</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3421,7 +3421,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D130">
-        <v>-3.938279390335083</v>
+        <v>-4.524019241333008</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3435,7 +3435,7 @@
         <v>-2</v>
       </c>
       <c r="D131">
-        <v>-1.251878380775452</v>
+        <v>-0.09054297208786011</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3449,7 +3449,7 @@
         <v>-1</v>
       </c>
       <c r="D132">
-        <v>-1.233106255531311</v>
+        <v>-2.818626880645752</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3463,7 +3463,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D133">
-        <v>-0.3780533671379089</v>
+        <v>-0.5965396761894226</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3477,7 +3477,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D134">
-        <v>-2.948119878768921</v>
+        <v>-2.725970506668091</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3491,7 +3491,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D135">
-        <v>-1.594935417175293</v>
+        <v>-1.442301034927368</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3505,7 +3505,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D136">
-        <v>-0.6486377120018005</v>
+        <v>-0.5230293273925781</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3519,7 +3519,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D137">
-        <v>-10.09712219238281</v>
+        <v>-10.09645652770996</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3533,7 +3533,7 @@
         <v>-3.5</v>
       </c>
       <c r="D138">
-        <v>1.094488859176636</v>
+        <v>-0.310754656791687</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3547,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="D139">
-        <v>8.046544075012207</v>
+        <v>6.768636703491211</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3561,7 +3561,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D140">
-        <v>-0.3724325299263</v>
+        <v>-0.5708395838737488</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3575,7 +3575,7 @@
         <v>-28.70000076293945</v>
       </c>
       <c r="D141">
-        <v>-17.98358917236328</v>
+        <v>-13.83711624145508</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3589,7 +3589,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D142">
-        <v>-4.013060569763184</v>
+        <v>-2.721284866333008</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3603,7 +3603,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D143">
-        <v>4.184324264526367</v>
+        <v>2.959749221801758</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3617,7 +3617,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D144">
-        <v>-2.937227010726929</v>
+        <v>-1.277724981307983</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3631,7 +3631,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D145">
-        <v>-8.643723487854004</v>
+        <v>-5.098653316497803</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3645,7 +3645,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D146">
-        <v>2.603811979293823</v>
+        <v>3.253024578094482</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3659,7 +3659,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D147">
-        <v>2.859872102737427</v>
+        <v>3.212491989135742</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3673,7 +3673,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D148">
-        <v>0.4706284403800964</v>
+        <v>0.2212572693824768</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3687,7 +3687,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D149">
-        <v>5.866168022155762</v>
+        <v>6.455718994140625</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3701,7 +3701,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D150">
-        <v>0.6710458993911743</v>
+        <v>0.1353000998497009</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3715,7 +3715,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D151">
-        <v>-6.726992607116699</v>
+        <v>-4.673398494720459</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3729,7 +3729,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D152">
-        <v>-9.542710304260254</v>
+        <v>-9.943785667419434</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3743,7 +3743,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D153">
-        <v>-6.7895188331604</v>
+        <v>-5.659364223480225</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3757,7 +3757,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D154">
-        <v>-3.309233427047729</v>
+        <v>-2.693518161773682</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3771,7 +3771,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D155">
-        <v>-0.2278303354978561</v>
+        <v>0.8829235434532166</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>0.06012384593486786</v>
+        <v>0.8411181569099426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3799,7 +3799,7 @@
         <v>26.29999923706055</v>
       </c>
       <c r="D157">
-        <v>17.94402885437012</v>
+        <v>17.09651565551758</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3813,7 +3813,7 @@
         <v>-16</v>
       </c>
       <c r="D158">
-        <v>-7.500681400299072</v>
+        <v>-7.681491374969482</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3827,7 +3827,7 @@
         <v>0.5</v>
       </c>
       <c r="D159">
-        <v>-3.135186910629272</v>
+        <v>-2.491461753845215</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3841,7 +3841,7 @@
         <v>27.79999923706055</v>
       </c>
       <c r="D160">
-        <v>11.96678447723389</v>
+        <v>13.33761119842529</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3855,7 +3855,7 @@
         <v>41.79999923706055</v>
       </c>
       <c r="D161">
-        <v>16.69464302062988</v>
+        <v>12.96066379547119</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3869,7 +3869,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D162">
-        <v>2.320816516876221</v>
+        <v>2.095940351486206</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3883,7 +3883,7 @@
         <v>0.5</v>
       </c>
       <c r="D163">
-        <v>1.486484289169312</v>
+        <v>1.691983461380005</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3897,7 +3897,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D164">
-        <v>-9.674656867980957</v>
+        <v>-10.49049854278564</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3911,7 +3911,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D165">
-        <v>-1.204504132270813</v>
+        <v>-4.377476692199707</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3925,7 +3925,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D166">
-        <v>-3.547128915786743</v>
+        <v>-1.954477548599243</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3939,7 +3939,7 @@
         <v>-5</v>
       </c>
       <c r="D167">
-        <v>-3.938444375991821</v>
+        <v>-3.308849334716797</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3953,7 +3953,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D168">
-        <v>-5.23382568359375</v>
+        <v>-4.682621002197266</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3967,7 +3967,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D169">
-        <v>-9.712250709533691</v>
+        <v>-9.959408760070801</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3981,7 +3981,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D170">
-        <v>2.519637823104858</v>
+        <v>2.331578731536865</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3995,7 +3995,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D171">
-        <v>-6.202342510223389</v>
+        <v>-7.2920823097229</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4009,7 +4009,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D172">
-        <v>1.837864637374878</v>
+        <v>1.569217681884766</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4023,7 +4023,7 @@
         <v>-18.20000076293945</v>
       </c>
       <c r="D173">
-        <v>-13.92924499511719</v>
+        <v>-12.50265884399414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4037,7 +4037,7 @@
         <v>-3</v>
       </c>
       <c r="D174">
-        <v>1.117443084716797</v>
+        <v>1.790468692779541</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4051,7 +4051,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D175">
-        <v>0.5837948322296143</v>
+        <v>-0.812416672706604</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4065,7 +4065,7 @@
         <v>-14</v>
       </c>
       <c r="D176">
-        <v>-9.172447204589844</v>
+        <v>-9.469034194946289</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4079,7 +4079,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D177">
-        <v>-2.941102266311646</v>
+        <v>-1.462300539016724</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4093,7 +4093,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D178">
-        <v>8.833968162536621</v>
+        <v>7.822709560394287</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4107,7 +4107,7 @@
         <v>-13.10000038146973</v>
       </c>
       <c r="D179">
-        <v>-7.837847709655762</v>
+        <v>-6.552605628967285</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4121,7 +4121,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D180">
-        <v>-10.65257549285889</v>
+        <v>-14.00255393981934</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4135,7 +4135,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D181">
-        <v>2.894392251968384</v>
+        <v>1.8580641746521</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4149,7 +4149,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D182">
-        <v>-0.1030178219079971</v>
+        <v>-0.4832445681095123</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4163,7 +4163,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D183">
-        <v>2.093764305114746</v>
+        <v>6.136986255645752</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4177,7 +4177,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D184">
-        <v>6.766806602478027</v>
+        <v>5.869678497314453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4191,7 +4191,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D185">
-        <v>1.529978513717651</v>
+        <v>1.424886703491211</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4205,7 +4205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D186">
-        <v>1.635164737701416</v>
+        <v>1.359458684921265</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4219,7 +4219,7 @@
         <v>-13.80000019073486</v>
       </c>
       <c r="D187">
-        <v>-10.43039226531982</v>
+        <v>-8.652628898620605</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4233,7 +4233,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D188">
-        <v>1.037413358688354</v>
+        <v>0.07647687196731567</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4247,7 +4247,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D189">
-        <v>1.06192409992218</v>
+        <v>3.16948413848877</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4261,7 +4261,7 @@
         <v>5.5</v>
       </c>
       <c r="D190">
-        <v>0.2033831924200058</v>
+        <v>1.131087303161621</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4275,7 +4275,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D191">
-        <v>-11.16950702667236</v>
+        <v>-10.85333442687988</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>1.94284462928772</v>
+        <v>1.266564130783081</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4303,7 +4303,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D193">
-        <v>2.479775667190552</v>
+        <v>2.634628534317017</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4317,7 +4317,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D194">
-        <v>-3.730267286300659</v>
+        <v>-4.089727401733398</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4331,7 +4331,7 @@
         <v>0.5</v>
       </c>
       <c r="D195">
-        <v>1.530158281326294</v>
+        <v>1.901835441589355</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4345,7 +4345,7 @@
         <v>32.59999847412109</v>
       </c>
       <c r="D196">
-        <v>19.40122413635254</v>
+        <v>18.62540054321289</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4359,7 +4359,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D197">
-        <v>8.555533409118652</v>
+        <v>7.297914505004883</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4373,7 +4373,7 @@
         <v>-22.89999961853027</v>
       </c>
       <c r="D198">
-        <v>-5.770058155059814</v>
+        <v>-3.255144119262695</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4387,7 +4387,7 @@
         <v>-20.89999961853027</v>
       </c>
       <c r="D199">
-        <v>-15.10222721099854</v>
+        <v>-13.82671928405762</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4401,7 +4401,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D200">
-        <v>1.573588013648987</v>
+        <v>0.5831689238548279</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4415,7 +4415,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D201">
-        <v>-3.01935887336731</v>
+        <v>-2.531854152679443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4429,7 +4429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D202">
-        <v>2.619834184646606</v>
+        <v>2.236449003219604</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4443,7 +4443,7 @@
         <v>-4.5</v>
       </c>
       <c r="D203">
-        <v>-1.06305718421936</v>
+        <v>-4.062485694885254</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4457,7 +4457,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D204">
-        <v>7.158588409423828</v>
+        <v>7.155153751373291</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4471,7 +4471,7 @@
         <v>-2.5</v>
       </c>
       <c r="D205">
-        <v>-1.021425247192383</v>
+        <v>-0.4952587485313416</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4485,7 +4485,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D206">
-        <v>4.651685237884521</v>
+        <v>2.63148021697998</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4499,7 +4499,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D207">
-        <v>4.42110538482666</v>
+        <v>5.501145839691162</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4513,7 +4513,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D208">
-        <v>-3.308041334152222</v>
+        <v>-0.4877003729343414</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4527,7 +4527,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D209">
-        <v>-2.732364892959595</v>
+        <v>-0.9740666151046753</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4541,7 +4541,7 @@
         <v>-4</v>
       </c>
       <c r="D210">
-        <v>1.094168424606323</v>
+        <v>-0.8711638450622559</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4555,7 +4555,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D211">
-        <v>1.793230295181274</v>
+        <v>2.108596563339233</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4569,7 +4569,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D212">
-        <v>-4.768908500671387</v>
+        <v>-5.413888931274414</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4583,7 +4583,7 @@
         <v>-6</v>
       </c>
       <c r="D213">
-        <v>-0.927117645740509</v>
+        <v>0.6480711102485657</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4597,7 +4597,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D214">
-        <v>1.021269798278809</v>
+        <v>0.4075048565864563</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4611,7 +4611,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D215">
-        <v>3.286320924758911</v>
+        <v>2.744531154632568</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4625,7 +4625,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D216">
-        <v>-1.558321356773376</v>
+        <v>-0.9211565256118774</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4639,7 +4639,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D217">
-        <v>-3.424111127853394</v>
+        <v>-2.175126075744629</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4653,7 +4653,7 @@
         <v>5.5</v>
       </c>
       <c r="D218">
-        <v>4.073961734771729</v>
+        <v>3.77170467376709</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4667,7 +4667,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D219">
-        <v>-0.2092311829328537</v>
+        <v>-0.8958603143692017</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4681,7 +4681,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D220">
-        <v>1.297539234161377</v>
+        <v>0.8678376078605652</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4695,7 +4695,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D221">
-        <v>1.463749885559082</v>
+        <v>1.926769018173218</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4709,7 +4709,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D222">
-        <v>-10.69788837432861</v>
+        <v>-10.68580913543701</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4723,7 +4723,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D223">
-        <v>4.242626190185547</v>
+        <v>4.231747150421143</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4737,7 +4737,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D224">
-        <v>-0.440338134765625</v>
+        <v>0.5441835522651672</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4751,7 +4751,7 @@
         <v>-25.79999923706055</v>
       </c>
       <c r="D225">
-        <v>-16.37327575683594</v>
+        <v>-13.15420150756836</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4765,7 +4765,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D226">
-        <v>5.088050842285156</v>
+        <v>4.707039356231689</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4779,7 +4779,7 @@
         <v>12</v>
       </c>
       <c r="D227">
-        <v>-6.203507423400879</v>
+        <v>-4.079433441162109</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4793,7 +4793,7 @@
         <v>-26.60000038146973</v>
       </c>
       <c r="D228">
-        <v>-15.00588512420654</v>
+        <v>-12.97444629669189</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4807,7 +4807,7 @@
         <v>-17.70000076293945</v>
       </c>
       <c r="D229">
-        <v>-14.82404041290283</v>
+        <v>-12.08546257019043</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4821,7 +4821,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D230">
-        <v>-7.095772266387939</v>
+        <v>-7.401919841766357</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4835,7 +4835,7 @@
         <v>-18.5</v>
       </c>
       <c r="D231">
-        <v>-15.89886379241943</v>
+        <v>-15.50597763061523</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4849,7 +4849,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D232">
-        <v>0.2358630150556564</v>
+        <v>0.3023657202720642</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4863,7 +4863,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D233">
-        <v>1.297306060791016</v>
+        <v>1.003237962722778</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4877,7 +4877,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D234">
-        <v>-1.18247652053833</v>
+        <v>-1.729810476303101</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4891,7 +4891,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D235">
-        <v>1.434571623802185</v>
+        <v>0.8874589800834656</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4905,7 +4905,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>-3.610606908798218</v>
+        <v>-2.532729148864746</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4919,7 +4919,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D237">
-        <v>5.596883773803711</v>
+        <v>1.193457126617432</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4933,7 +4933,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D238">
-        <v>-2.348015308380127</v>
+        <v>-0.7861218452453613</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4947,7 +4947,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D239">
-        <v>4.939981460571289</v>
+        <v>3.52981424331665</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4961,7 +4961,7 @@
         <v>5.5</v>
       </c>
       <c r="D240">
-        <v>2.811285734176636</v>
+        <v>3.503030776977539</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4975,7 +4975,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D241">
-        <v>1.585520505905151</v>
+        <v>2.478599309921265</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4989,7 +4989,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D242">
-        <v>-0.1973584741353989</v>
+        <v>-5.789828777313232</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5003,7 +5003,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D243">
-        <v>1.917012691497803</v>
+        <v>1.532734394073486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5017,7 +5017,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D244">
-        <v>2.013104438781738</v>
+        <v>1.46323299407959</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5031,7 +5031,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D245">
-        <v>-2.908267974853516</v>
+        <v>-2.135172128677368</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5045,7 +5045,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D246">
-        <v>2.215818881988525</v>
+        <v>2.549897432327271</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5059,7 +5059,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D247">
-        <v>2.600243091583252</v>
+        <v>1.796043872833252</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5073,7 +5073,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D248">
-        <v>-5.458208084106445</v>
+        <v>-7.020355701446533</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5087,7 +5087,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D249">
-        <v>-1.14067018032074</v>
+        <v>-2.14725399017334</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5101,7 +5101,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D250">
-        <v>-3.7824866771698</v>
+        <v>-2.949048519134521</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5115,7 +5115,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D251">
-        <v>7.138701438903809</v>
+        <v>4.349024295806885</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5129,7 +5129,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>1.689584493637085</v>
+        <v>1.748987436294556</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5143,7 +5143,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D253">
-        <v>-4.405920028686523</v>
+        <v>-3.074568510055542</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5157,7 +5157,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D254">
-        <v>6.95207405090332</v>
+        <v>6.976112842559814</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5171,7 +5171,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D255">
-        <v>3.476635217666626</v>
+        <v>2.952364206314087</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5185,7 +5185,7 @@
         <v>-7.5</v>
       </c>
       <c r="D256">
-        <v>-4.222111225128174</v>
+        <v>-5.544907093048096</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5199,7 +5199,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D257">
-        <v>1.524572610855103</v>
+        <v>0.5513470768928528</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5213,7 +5213,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D258">
-        <v>2.049935340881348</v>
+        <v>2.1856689453125</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5227,7 +5227,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D259">
-        <v>-0.7034940123558044</v>
+        <v>-0.9059394598007202</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5241,7 +5241,7 @@
         <v>-7</v>
       </c>
       <c r="D260">
-        <v>-6.483154296875</v>
+        <v>-6.537954807281494</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5255,7 +5255,7 @@
         <v>-13.69999980926514</v>
       </c>
       <c r="D261">
-        <v>-10.24375820159912</v>
+        <v>-10.5534029006958</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5269,7 +5269,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D262">
-        <v>3.135621786117554</v>
+        <v>3.236575126647949</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5283,7 +5283,7 @@
         <v>3.5</v>
       </c>
       <c r="D263">
-        <v>2.057798624038696</v>
+        <v>1.302664756774902</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5297,7 +5297,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D264">
-        <v>1.428106069564819</v>
+        <v>0.2432103157043457</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5311,7 +5311,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D265">
-        <v>-12.44183444976807</v>
+        <v>-10.72420310974121</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5325,7 +5325,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D266">
-        <v>0.9250860810279846</v>
+        <v>0.487974226474762</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5339,7 +5339,7 @@
         <v>-14</v>
       </c>
       <c r="D267">
-        <v>-5.75813102722168</v>
+        <v>-5.084928035736084</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5353,7 +5353,7 @@
         <v>3.5</v>
       </c>
       <c r="D268">
-        <v>-1.362427830696106</v>
+        <v>-0.7504396438598633</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5367,7 +5367,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D269">
-        <v>-5.306124687194824</v>
+        <v>-5.476412296295166</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5381,7 +5381,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>0.5598675608634949</v>
+        <v>0.3344581723213196</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5395,7 +5395,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D271">
-        <v>-1.318297386169434</v>
+        <v>-1.014494895935059</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5409,7 +5409,7 @@
         <v>-22.29999923706055</v>
       </c>
       <c r="D272">
-        <v>-13.88498973846436</v>
+        <v>-12.14114761352539</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5423,7 +5423,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D273">
-        <v>4.958930492401123</v>
+        <v>2.315151691436768</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5437,7 +5437,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D274">
-        <v>-14.18103408813477</v>
+        <v>-11.05419731140137</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5451,7 +5451,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D275">
-        <v>2.288197040557861</v>
+        <v>1.273478984832764</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5465,7 +5465,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D276">
-        <v>0.5409253239631653</v>
+        <v>-4.089792251586914</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5479,7 +5479,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D277">
-        <v>3.502386093139648</v>
+        <v>2.194375991821289</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5493,7 +5493,7 @@
         <v>5.5</v>
       </c>
       <c r="D278">
-        <v>2.160627126693726</v>
+        <v>1.74961519241333</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5507,7 +5507,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D279">
-        <v>3.308616638183594</v>
+        <v>2.797124862670898</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5521,7 +5521,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D280">
-        <v>-18.37587928771973</v>
+        <v>-12.26510429382324</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5535,7 +5535,7 @@
         <v>-19</v>
       </c>
       <c r="D281">
-        <v>-13.3376932144165</v>
+        <v>-12.6935863494873</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5549,7 +5549,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D282">
-        <v>1.743629455566406</v>
+        <v>1.203991413116455</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5563,7 +5563,7 @@
         <v>-2.5</v>
       </c>
       <c r="D283">
-        <v>-3.216554880142212</v>
+        <v>-3.567359447479248</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5577,7 +5577,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D284">
-        <v>1.92881178855896</v>
+        <v>0.9247247576713562</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5591,7 +5591,7 @@
         <v>-7</v>
       </c>
       <c r="D285">
-        <v>-5.581396102905273</v>
+        <v>-4.157310485839844</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5605,7 +5605,7 @@
         <v>-16.79999923706055</v>
       </c>
       <c r="D286">
-        <v>-12.61014366149902</v>
+        <v>-8.36457633972168</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5619,7 +5619,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D287">
-        <v>1.680264353752136</v>
+        <v>1.693769693374634</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5633,7 +5633,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D288">
-        <v>1.993761301040649</v>
+        <v>3.874086380004883</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5647,7 +5647,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D289">
-        <v>9.477314949035645</v>
+        <v>8.877927780151367</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5661,7 +5661,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D290">
-        <v>0.4452985525131226</v>
+        <v>1.603940010070801</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5675,7 +5675,7 @@
         <v>-27.39999961853027</v>
       </c>
       <c r="D291">
-        <v>-18.72574043273926</v>
+        <v>-17.98100852966309</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5689,7 +5689,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D292">
-        <v>-3.927522897720337</v>
+        <v>-2.042947053909302</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5703,7 +5703,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>-0.6845439672470093</v>
+        <v>0.06852096319198608</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5717,7 +5717,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D294">
-        <v>0.5537788271903992</v>
+        <v>3.089329957962036</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5731,7 +5731,7 @@
         <v>-4</v>
       </c>
       <c r="D295">
-        <v>-8.842223167419434</v>
+        <v>-9.299992561340332</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5745,7 +5745,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D296">
-        <v>-15.34604644775391</v>
+        <v>-14.27628803253174</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5759,7 +5759,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D297">
-        <v>2.374047994613647</v>
+        <v>4.164937019348145</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5773,7 +5773,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D298">
-        <v>-2.082480430603027</v>
+        <v>-2.622839689254761</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5787,7 +5787,7 @@
         <v>-20</v>
       </c>
       <c r="D299">
-        <v>-14.82828903198242</v>
+        <v>-14.30392742156982</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5801,7 +5801,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D300">
-        <v>-12.66718673706055</v>
+        <v>-10.22177505493164</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5815,7 +5815,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D301">
-        <v>-3.188288450241089</v>
+        <v>-3.337563037872314</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5829,7 +5829,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D302">
-        <v>-0.1240444034337997</v>
+        <v>-1.281423091888428</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5843,7 +5843,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D303">
-        <v>1.000360727310181</v>
+        <v>-0.1408556699752808</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5857,7 +5857,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D304">
-        <v>0.5491494536399841</v>
+        <v>0.3665208220481873</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5871,7 +5871,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D305">
-        <v>8.796857833862305</v>
+        <v>9.644065856933594</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5885,7 +5885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D306">
-        <v>1.175897121429443</v>
+        <v>1.211105585098267</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5899,7 +5899,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D307">
-        <v>-6.239616870880127</v>
+        <v>-6.94914436340332</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>0.4649205803871155</v>
+        <v>1.263745307922363</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5927,7 +5927,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D309">
-        <v>-1.731782913208008</v>
+        <v>-3.245317459106445</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5941,7 +5941,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D310">
-        <v>2.289674520492554</v>
+        <v>1.272966861724854</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5955,7 +5955,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D311">
-        <v>1.585333228111267</v>
+        <v>0.9232372641563416</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5969,7 +5969,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D312">
-        <v>5.095181941986084</v>
+        <v>3.668086528778076</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5983,7 +5983,7 @@
         <v>-18</v>
       </c>
       <c r="D313">
-        <v>-13.26550483703613</v>
+        <v>-13.06960296630859</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5997,7 +5997,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D314">
-        <v>-3.413406610488892</v>
+        <v>-4.608006477355957</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6011,7 +6011,7 @@
         <v>-1.5</v>
       </c>
       <c r="D315">
-        <v>0.1506745666265488</v>
+        <v>0.1347751021385193</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6025,7 +6025,7 @@
         <v>-13.10000038146973</v>
       </c>
       <c r="D316">
-        <v>-5.33782434463501</v>
+        <v>-5.140720367431641</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6039,7 +6039,7 @@
         <v>-33.90000152587891</v>
       </c>
       <c r="D317">
-        <v>-24.07744789123535</v>
+        <v>-21.08010864257812</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6053,7 +6053,7 @@
         <v>-19.89999961853027</v>
       </c>
       <c r="D318">
-        <v>-14.13025760650635</v>
+        <v>-12.07498550415039</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6067,7 +6067,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D319">
-        <v>-0.02991907298564911</v>
+        <v>-2.456438541412354</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6081,7 +6081,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D320">
-        <v>-0.1360860615968704</v>
+        <v>1.853468418121338</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6095,7 +6095,7 @@
         <v>0.5</v>
       </c>
       <c r="D321">
-        <v>0.8709027171134949</v>
+        <v>-3.579259157180786</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6109,7 +6109,7 @@
         <v>-9.399999618530273</v>
       </c>
       <c r="D322">
-        <v>-9.324860572814941</v>
+        <v>-9.111825942993164</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6123,7 +6123,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D323">
-        <v>-3.764085054397583</v>
+        <v>-3.88314414024353</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6137,7 +6137,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D324">
-        <v>2.522577524185181</v>
+        <v>0.8752461075782776</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6151,7 +6151,7 @@
         <v>8.5</v>
       </c>
       <c r="D325">
-        <v>0.2361577898263931</v>
+        <v>1.372862815856934</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6165,7 +6165,7 @@
         <v>-24.79999923706055</v>
       </c>
       <c r="D326">
-        <v>-17.6383228302002</v>
+        <v>-19.29262351989746</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6179,7 +6179,7 @@
         <v>11</v>
       </c>
       <c r="D327">
-        <v>3.780002117156982</v>
+        <v>3.625630378723145</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6193,7 +6193,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D328">
-        <v>-4.184350490570068</v>
+        <v>-1.931413173675537</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6207,7 +6207,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D329">
-        <v>-0.4450215697288513</v>
+        <v>-0.1400522589683533</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6221,7 +6221,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D330">
-        <v>4.979366779327393</v>
+        <v>3.780934810638428</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6235,7 +6235,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D331">
-        <v>-0.682045578956604</v>
+        <v>-1.618794441223145</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6249,7 +6249,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D332">
-        <v>4.341108798980713</v>
+        <v>2.842768669128418</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6263,7 +6263,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D333">
-        <v>-2.074948310852051</v>
+        <v>-1.698922395706177</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6277,7 +6277,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D334">
-        <v>-3.937719106674194</v>
+        <v>-2.407784223556519</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6291,7 +6291,7 @@
         <v>-30.60000038146973</v>
       </c>
       <c r="D335">
-        <v>-20.42096138000488</v>
+        <v>-20.05319786071777</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6305,7 +6305,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D336">
-        <v>-5.641563892364502</v>
+        <v>-6.265957832336426</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6319,7 +6319,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D337">
-        <v>6.473196506500244</v>
+        <v>7.66879415512085</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6333,7 +6333,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D338">
-        <v>-0.4087653756141663</v>
+        <v>-1.06778359413147</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6347,7 +6347,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D339">
-        <v>-4.116104125976562</v>
+        <v>-4.836495876312256</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6361,7 +6361,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D340">
-        <v>-11.14478969573975</v>
+        <v>-10.62249660491943</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6375,7 +6375,7 @@
         <v>-24.20000076293945</v>
       </c>
       <c r="D341">
-        <v>-21.97353744506836</v>
+        <v>-21.64996528625488</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6389,7 +6389,7 @@
         <v>-12.5</v>
       </c>
       <c r="D342">
-        <v>-8.68448543548584</v>
+        <v>-8.696852684020996</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6403,7 +6403,7 @@
         <v>-34.5</v>
       </c>
       <c r="D343">
-        <v>-22.83356285095215</v>
+        <v>-18.83062934875488</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6417,7 +6417,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D344">
-        <v>1.623284339904785</v>
+        <v>0.3537386059761047</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6431,7 +6431,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D345">
-        <v>3.337888956069946</v>
+        <v>2.452643871307373</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6445,7 +6445,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D346">
-        <v>5.446869850158691</v>
+        <v>5.000594139099121</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6459,7 +6459,7 @@
         <v>2.5</v>
       </c>
       <c r="D347">
-        <v>1.605621337890625</v>
+        <v>1.797541618347168</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6473,7 +6473,7 @@
         <v>-22.60000038146973</v>
       </c>
       <c r="D348">
-        <v>-16.02263832092285</v>
+        <v>-14.51704788208008</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6487,7 +6487,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D349">
-        <v>0.1652294546365738</v>
+        <v>1.205321550369263</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6501,7 +6501,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D350">
-        <v>-4.36845588684082</v>
+        <v>-3.086416482925415</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6515,7 +6515,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D351">
-        <v>0.7747933268547058</v>
+        <v>-0.0405585765838623</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6529,7 +6529,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D352">
-        <v>-4.961489200592041</v>
+        <v>-3.82044506072998</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6543,7 +6543,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D353">
-        <v>0.304452121257782</v>
+        <v>1.539200067520142</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6557,7 +6557,7 @@
         <v>-18.5</v>
       </c>
       <c r="D354">
-        <v>-14.05849552154541</v>
+        <v>-14.47367477416992</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6571,7 +6571,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D355">
-        <v>-4.798666000366211</v>
+        <v>-3.09416675567627</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6585,7 +6585,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D356">
-        <v>1.175475120544434</v>
+        <v>2.088204145431519</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6599,7 +6599,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D357">
-        <v>-0.8692905902862549</v>
+        <v>0.7779508233070374</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6613,7 +6613,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D358">
-        <v>-12.46352577209473</v>
+        <v>-11.03425884246826</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6627,7 +6627,7 @@
         <v>-19.5</v>
       </c>
       <c r="D359">
-        <v>-13.56750392913818</v>
+        <v>-11.33562278747559</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6641,7 +6641,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D360">
-        <v>3.556735277175903</v>
+        <v>2.199758529663086</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6655,7 +6655,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D361">
-        <v>1.130956053733826</v>
+        <v>0.4643719792366028</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6669,7 +6669,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D362">
-        <v>2.287339925765991</v>
+        <v>1.108040332794189</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6683,7 +6683,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D363">
-        <v>-7.757518768310547</v>
+        <v>-5.052022457122803</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6697,7 +6697,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D364">
-        <v>-1.412402153015137</v>
+        <v>0.6451855301856995</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6711,7 +6711,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D365">
-        <v>-5.714628219604492</v>
+        <v>-5.767486095428467</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6725,7 +6725,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D366">
-        <v>6.602128028869629</v>
+        <v>11.33317947387695</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6739,7 +6739,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D367">
-        <v>1.292402982711792</v>
+        <v>0.9736930727958679</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6753,7 +6753,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D368">
-        <v>-0.8708626627922058</v>
+        <v>-4.09187650680542</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6767,7 +6767,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D369">
-        <v>-9.648152351379395</v>
+        <v>-10.18085384368896</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6781,7 +6781,7 @@
         <v>-30.79999923706055</v>
       </c>
       <c r="D370">
-        <v>-21.57350540161133</v>
+        <v>-15.74122428894043</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6795,7 +6795,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D371">
-        <v>2.595027685165405</v>
+        <v>0.8261941075325012</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6809,7 +6809,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D372">
-        <v>-4.759510040283203</v>
+        <v>-5.719400405883789</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6823,7 +6823,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D373">
-        <v>-2.486715793609619</v>
+        <v>-1.208490490913391</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6837,7 +6837,7 @@
         <v>4.5</v>
       </c>
       <c r="D374">
-        <v>3.31272029876709</v>
+        <v>2.626176595687866</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6851,7 +6851,7 @@
         <v>-2.5</v>
       </c>
       <c r="D375">
-        <v>-12.10908699035645</v>
+        <v>-13.27311706542969</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6865,7 +6865,7 @@
         <v>-31</v>
       </c>
       <c r="D376">
-        <v>-18.64292335510254</v>
+        <v>-13.60589122772217</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6879,7 +6879,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D377">
-        <v>1.110338926315308</v>
+        <v>1.017562389373779</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="D378">
-        <v>0.8941319584846497</v>
+        <v>0.6225336194038391</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6907,7 +6907,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D379">
-        <v>3.732162714004517</v>
+        <v>3.738088607788086</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6921,7 +6921,7 @@
         <v>5</v>
       </c>
       <c r="D380">
-        <v>4.898733139038086</v>
+        <v>1.639321327209473</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6935,7 +6935,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D381">
-        <v>0.3071702718734741</v>
+        <v>1.01285982131958</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6949,7 +6949,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D382">
-        <v>-10.02575016021729</v>
+        <v>-6.742053031921387</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6963,7 +6963,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D383">
-        <v>5.534636497497559</v>
+        <v>4.34843111038208</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6977,7 +6977,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D384">
-        <v>11.37981414794922</v>
+        <v>10.53093242645264</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6991,7 +6991,7 @@
         <v>-30.89999961853027</v>
       </c>
       <c r="D385">
-        <v>-20.40262794494629</v>
+        <v>-18.93563652038574</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7005,7 +7005,7 @@
         <v>-3</v>
       </c>
       <c r="D386">
-        <v>1.328747510910034</v>
+        <v>0.9309783577919006</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7019,7 +7019,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>2.328787565231323</v>
+        <v>2.805470943450928</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7033,7 +7033,7 @@
         <v>-6</v>
       </c>
       <c r="D388">
-        <v>-0.8690665364265442</v>
+        <v>-0.5377321839332581</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7047,7 +7047,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D389">
-        <v>-3.182067394256592</v>
+        <v>-1.209309101104736</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7061,7 +7061,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D390">
-        <v>3.828469038009644</v>
+        <v>2.428106307983398</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7075,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>4.474031448364258</v>
+        <v>3.754973888397217</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7089,7 +7089,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D392">
-        <v>-0.2627728581428528</v>
+        <v>-2.33577299118042</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7103,7 +7103,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D393">
-        <v>-1.329708099365234</v>
+        <v>0.3561972975730896</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7117,7 +7117,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D394">
-        <v>1.761769652366638</v>
+        <v>1.294677257537842</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7131,7 +7131,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D395">
-        <v>-3.919039249420166</v>
+        <v>-4.866998195648193</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7145,7 +7145,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D396">
-        <v>1.313009262084961</v>
+        <v>2.226115942001343</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7159,7 +7159,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D397">
-        <v>1.954317808151245</v>
+        <v>1.233288049697876</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7173,7 +7173,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D398">
-        <v>-1.135349631309509</v>
+        <v>-0.2604922652244568</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7187,7 +7187,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D399">
-        <v>-13.64378929138184</v>
+        <v>-11.90695571899414</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7201,7 +7201,7 @@
         <v>8</v>
       </c>
       <c r="D400">
-        <v>0.6024371385574341</v>
+        <v>1.54319429397583</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7215,7 +7215,7 @@
         <v>-11</v>
       </c>
       <c r="D401">
-        <v>-6.794862747192383</v>
+        <v>-5.232945919036865</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7229,7 +7229,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D402">
-        <v>3.831353425979614</v>
+        <v>4.534029006958008</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7243,7 +7243,7 @@
         <v>-22.79999923706055</v>
       </c>
       <c r="D403">
-        <v>-22.1157054901123</v>
+        <v>-16.93066024780273</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7257,7 +7257,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D404">
-        <v>-0.8594626188278198</v>
+        <v>-0.1636266112327576</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7271,7 +7271,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D405">
-        <v>3.57986855506897</v>
+        <v>3.031387567520142</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7285,7 +7285,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D406">
-        <v>-7.254173278808594</v>
+        <v>-5.914843082427979</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7299,7 +7299,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D407">
-        <v>-9.089807510375977</v>
+        <v>-7.348363399505615</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7313,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>3.127931594848633</v>
+        <v>2.874338150024414</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7327,7 +7327,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D409">
-        <v>1.535557985305786</v>
+        <v>1.239505529403687</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7341,7 +7341,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D410">
-        <v>0.5782302021980286</v>
+        <v>0.2982730865478516</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7355,7 +7355,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D411">
-        <v>2.400035858154297</v>
+        <v>1.222100973129272</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7369,7 +7369,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D412">
-        <v>3.362733840942383</v>
+        <v>1.430049180984497</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7383,7 +7383,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D413">
-        <v>-4.751796722412109</v>
+        <v>-1.358640670776367</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7397,7 +7397,7 @@
         <v>-14.60000038146973</v>
       </c>
       <c r="D414">
-        <v>-11.85917186737061</v>
+        <v>-11.33015060424805</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7411,7 +7411,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D415">
-        <v>-3.405627250671387</v>
+        <v>-1.049193859100342</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7425,7 +7425,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D416">
-        <v>2.627236604690552</v>
+        <v>2.788305282592773</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7439,7 +7439,7 @@
         <v>-9</v>
       </c>
       <c r="D417">
-        <v>-1.314467906951904</v>
+        <v>-0.5700530409812927</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7453,7 +7453,7 @@
         <v>-32.20000076293945</v>
       </c>
       <c r="D418">
-        <v>-29.14043998718262</v>
+        <v>-28.96608734130859</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7467,7 +7467,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D419">
-        <v>-15.58697700500488</v>
+        <v>-13.78792572021484</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7481,7 +7481,7 @@
         <v>2</v>
       </c>
       <c r="D420">
-        <v>2.431237459182739</v>
+        <v>1.980473041534424</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7495,7 +7495,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D421">
-        <v>3.933021783828735</v>
+        <v>3.769947528839111</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7509,7 +7509,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D422">
-        <v>9.829913139343262</v>
+        <v>9.852115631103516</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7523,7 +7523,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D423">
-        <v>-0.1334826201200485</v>
+        <v>-0.5022199749946594</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7537,7 +7537,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D424">
-        <v>-1.812946319580078</v>
+        <v>-1.740888833999634</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7551,7 +7551,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D425">
-        <v>2.944617748260498</v>
+        <v>0.4720062613487244</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7565,7 +7565,7 @@
         <v>-30.29999923706055</v>
       </c>
       <c r="D426">
-        <v>-19.86265754699707</v>
+        <v>-17.13615989685059</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7579,7 +7579,7 @@
         <v>-16</v>
       </c>
       <c r="D427">
-        <v>-8.960814476013184</v>
+        <v>-8.624980926513672</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7593,7 +7593,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D428">
-        <v>-0.1337663978338242</v>
+        <v>-0.5255423784255981</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7607,7 +7607,7 @@
         <v>-14.30000019073486</v>
       </c>
       <c r="D429">
-        <v>-5.662689685821533</v>
+        <v>-7.35598611831665</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7621,7 +7621,7 @@
         <v>-11.5</v>
       </c>
       <c r="D430">
-        <v>-9.606931686401367</v>
+        <v>-7.147417068481445</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7635,7 +7635,7 @@
         <v>-2.5</v>
       </c>
       <c r="D431">
-        <v>-1.792763113975525</v>
+        <v>-2.440386533737183</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7649,7 +7649,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>-0.5963388681411743</v>
+        <v>0.2961375117301941</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7663,7 +7663,7 @@
         <v>-4</v>
       </c>
       <c r="D433">
-        <v>2.455415010452271</v>
+        <v>1.218668222427368</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7677,7 +7677,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D434">
-        <v>-0.2327846586704254</v>
+        <v>0.9734295010566711</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="D435">
-        <v>-0.3196715712547302</v>
+        <v>0.2484275698661804</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7705,7 +7705,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D436">
-        <v>1.280745387077332</v>
+        <v>0.9471736550331116</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7719,7 +7719,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D437">
-        <v>1.638239860534668</v>
+        <v>1.378810882568359</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7733,7 +7733,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D438">
-        <v>1.209617614746094</v>
+        <v>0.798767626285553</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7747,7 +7747,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D439">
-        <v>2.576465845108032</v>
+        <v>1.680848121643066</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7761,7 +7761,7 @@
         <v>-2</v>
       </c>
       <c r="D440">
-        <v>-0.09474296867847443</v>
+        <v>0.3714389204978943</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7775,7 +7775,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D441">
-        <v>3.035559415817261</v>
+        <v>2.807712554931641</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7789,7 +7789,7 @@
         <v>-1</v>
       </c>
       <c r="D442">
-        <v>-3.792822122573853</v>
+        <v>-0.6387844681739807</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7803,7 +7803,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D443">
-        <v>-7.431795120239258</v>
+        <v>-4.390989780426025</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7817,7 +7817,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D444">
-        <v>16.90348052978516</v>
+        <v>18.10574150085449</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7831,7 +7831,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D445">
-        <v>6.420200347900391</v>
+        <v>10.12007904052734</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7845,7 +7845,7 @@
         <v>4</v>
       </c>
       <c r="D446">
-        <v>0.3611622452735901</v>
+        <v>0.3999877572059631</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7859,7 +7859,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D447">
-        <v>14.69359874725342</v>
+        <v>14.98673915863037</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7873,7 +7873,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D448">
-        <v>1.747513055801392</v>
+        <v>1.019392490386963</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7887,7 +7887,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D449">
-        <v>5.653497695922852</v>
+        <v>5.347840309143066</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7901,7 +7901,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D450">
-        <v>-0.7914227843284607</v>
+        <v>-0.8228972554206848</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7915,7 +7915,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D451">
-        <v>-16.48625564575195</v>
+        <v>-13.61201286315918</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7929,7 +7929,7 @@
         <v>-4</v>
       </c>
       <c r="D452">
-        <v>-2.422342538833618</v>
+        <v>-2.147986888885498</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7943,7 +7943,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D453">
-        <v>-7.951272487640381</v>
+        <v>-1.928087472915649</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7957,7 +7957,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D454">
-        <v>1.827764511108398</v>
+        <v>1.253247499465942</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7971,7 +7971,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D455">
-        <v>-6.579333782196045</v>
+        <v>-4.763307094573975</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7985,7 +7985,7 @@
         <v>33.5</v>
       </c>
       <c r="D456">
-        <v>22.4676513671875</v>
+        <v>26.76734352111816</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7999,7 +7999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D457">
-        <v>2.446105718612671</v>
+        <v>3.031715869903564</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8013,7 +8013,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D458">
-        <v>-2.808669328689575</v>
+        <v>-1.423469305038452</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8027,7 +8027,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D459">
-        <v>-4.080709934234619</v>
+        <v>-3.116691112518311</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8041,7 +8041,7 @@
         <v>-5</v>
       </c>
       <c r="D460">
-        <v>1.4268878698349</v>
+        <v>1.512224674224854</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8055,7 +8055,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D461">
-        <v>-1.076709747314453</v>
+        <v>-1.402949810028076</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8069,7 +8069,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D462">
-        <v>-1.213074326515198</v>
+        <v>-3.41807746887207</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8083,7 +8083,7 @@
         <v>-2</v>
       </c>
       <c r="D463">
-        <v>-1.017275452613831</v>
+        <v>0.3328074812889099</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8097,7 +8097,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>1.861724138259888</v>
+        <v>0.009594142436981201</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8111,7 +8111,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D465">
-        <v>-11.8486909866333</v>
+        <v>-10.75864410400391</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8125,7 +8125,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D466">
-        <v>-0.252240002155304</v>
+        <v>0.7805010676383972</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8139,7 +8139,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D467">
-        <v>3.62123441696167</v>
+        <v>1.769351005554199</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8153,7 +8153,7 @@
         <v>-6.5</v>
       </c>
       <c r="D468">
-        <v>-4.107470035552979</v>
+        <v>-5.062230110168457</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8167,7 +8167,7 @@
         <v>14</v>
       </c>
       <c r="D469">
-        <v>-1.893790006637573</v>
+        <v>1.821101665496826</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8181,7 +8181,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D470">
-        <v>-0.6527521014213562</v>
+        <v>1.048308134078979</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8195,7 +8195,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D471">
-        <v>-2.77038836479187</v>
+        <v>0.1367177367210388</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8209,7 +8209,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D472">
-        <v>-4.631425857543945</v>
+        <v>-4.740801334381104</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8223,7 +8223,7 @@
         <v>-0.5</v>
       </c>
       <c r="D473">
-        <v>1.742523550987244</v>
+        <v>2.383548736572266</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8237,7 +8237,7 @@
         <v>5.5</v>
       </c>
       <c r="D474">
-        <v>4.071614265441895</v>
+        <v>3.308740139007568</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8251,7 +8251,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D475">
-        <v>9.48941707611084</v>
+        <v>10.37933349609375</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8265,7 +8265,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D476">
-        <v>-8.760403633117676</v>
+        <v>-6.458756923675537</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8279,7 +8279,7 @@
         <v>-8.5</v>
       </c>
       <c r="D477">
-        <v>-7.264129161834717</v>
+        <v>-8.451169013977051</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8293,7 +8293,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D478">
-        <v>0.8402001261711121</v>
+        <v>1.086703777313232</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8307,7 +8307,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D479">
-        <v>-10.47163772583008</v>
+        <v>-5.894004344940186</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8321,7 +8321,7 @@
         <v>-5</v>
       </c>
       <c r="D480">
-        <v>1.599425196647644</v>
+        <v>1.362048387527466</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8335,7 +8335,7 @@
         <v>1.5</v>
       </c>
       <c r="D481">
-        <v>1.909050226211548</v>
+        <v>0.6376639008522034</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8349,7 +8349,7 @@
         <v>-6.5</v>
       </c>
       <c r="D482">
-        <v>-7.557437419891357</v>
+        <v>-6.22843599319458</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8363,7 +8363,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D483">
-        <v>0.1194182187318802</v>
+        <v>0.7401338219642639</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8377,7 +8377,7 @@
         <v>0.5</v>
       </c>
       <c r="D484">
-        <v>2.052221536636353</v>
+        <v>2.823494672775269</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8391,7 +8391,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D485">
-        <v>2.077881574630737</v>
+        <v>2.379238843917847</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8405,7 +8405,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D486">
-        <v>1.053098678588867</v>
+        <v>0.6519318222999573</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8419,7 +8419,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D487">
-        <v>-9.182160377502441</v>
+        <v>-9.560173034667969</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8433,7 +8433,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D488">
-        <v>9.810897827148438</v>
+        <v>9.106266021728516</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8447,7 +8447,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>2.458127021789551</v>
+        <v>1.314056158065796</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8461,7 +8461,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D490">
-        <v>-6.038307666778564</v>
+        <v>-4.576799392700195</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8475,7 +8475,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D491">
-        <v>-4.736063003540039</v>
+        <v>-7.599705696105957</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8489,7 +8489,7 @@
         <v>5.5</v>
       </c>
       <c r="D492">
-        <v>1.74004852771759</v>
+        <v>1.535431861877441</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8503,7 +8503,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D493">
-        <v>0.8839733004570007</v>
+        <v>1.158528327941895</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8517,7 +8517,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D494">
-        <v>-1.053972005844116</v>
+        <v>-3.697842121124268</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8531,7 +8531,7 @@
         <v>-1</v>
       </c>
       <c r="D495">
-        <v>-1.608562350273132</v>
+        <v>-2.053091287612915</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8545,7 +8545,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D496">
-        <v>-0.8502113223075867</v>
+        <v>-0.5095417499542236</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8559,7 +8559,7 @@
         <v>-14.30000019073486</v>
       </c>
       <c r="D497">
-        <v>-14.32730960845947</v>
+        <v>-10.49997425079346</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8573,7 +8573,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D498">
-        <v>-6.422093391418457</v>
+        <v>-5.320216655731201</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8587,7 +8587,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D499">
-        <v>2.116660118103027</v>
+        <v>1.794440746307373</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8601,7 +8601,7 @@
         <v>-3.5</v>
       </c>
       <c r="D500">
-        <v>-3.394474744796753</v>
+        <v>-3.018592834472656</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8615,7 +8615,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D501">
-        <v>6.169017314910889</v>
+        <v>3.559373378753662</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8629,7 +8629,7 @@
         <v>10.5</v>
       </c>
       <c r="D502">
-        <v>7.002994537353516</v>
+        <v>6.337227344512939</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8643,7 +8643,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D503">
-        <v>-6.099630355834961</v>
+        <v>-5.699056625366211</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8657,7 +8657,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D504">
-        <v>2.180757761001587</v>
+        <v>1.202265501022339</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8671,7 +8671,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D505">
-        <v>-3.787812232971191</v>
+        <v>-5.614717960357666</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8685,7 +8685,7 @@
         <v>22</v>
       </c>
       <c r="D506">
-        <v>14.09019947052002</v>
+        <v>18.61663246154785</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8699,7 +8699,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D507">
-        <v>-6.08902645111084</v>
+        <v>-3.838135242462158</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8713,7 +8713,7 @@
         <v>-4.5</v>
       </c>
       <c r="D508">
-        <v>0.8276748061180115</v>
+        <v>-1.912030458450317</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8727,7 +8727,7 @@
         <v>-5.5</v>
       </c>
       <c r="D509">
-        <v>2.338859558105469</v>
+        <v>1.94763970375061</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8741,7 +8741,7 @@
         <v>-6.5</v>
       </c>
       <c r="D510">
-        <v>-10.64745616912842</v>
+        <v>-10.84103012084961</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="D511">
-        <v>1.398610591888428</v>
+        <v>1.335710525512695</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8769,7 +8769,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D512">
-        <v>11.30003070831299</v>
+        <v>8.139554023742676</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8783,7 +8783,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D513">
-        <v>1.194585680961609</v>
+        <v>-0.3442909419536591</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8797,7 +8797,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D514">
-        <v>2.46657657623291</v>
+        <v>2.395968914031982</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8811,7 +8811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>1.316184997558594</v>
+        <v>0.813174307346344</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8825,7 +8825,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D516">
-        <v>3.693755626678467</v>
+        <v>2.678961753845215</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8839,7 +8839,7 @@
         <v>-25.60000038146973</v>
       </c>
       <c r="D517">
-        <v>-11.74754333496094</v>
+        <v>-10.46475028991699</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8853,7 +8853,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D518">
-        <v>5.922356605529785</v>
+        <v>4.663578510284424</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8867,7 +8867,7 @@
         <v>3.5</v>
       </c>
       <c r="D519">
-        <v>1.243826389312744</v>
+        <v>0.7551677823066711</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="D520">
-        <v>4.988067150115967</v>
+        <v>7.331915378570557</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8895,7 +8895,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D521">
-        <v>2.110442399978638</v>
+        <v>-7.163168430328369</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8909,7 +8909,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D522">
-        <v>2.227882623672485</v>
+        <v>-0.5526672601699829</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8923,7 +8923,7 @@
         <v>13.39999961853027</v>
       </c>
       <c r="D523">
-        <v>8.498160362243652</v>
+        <v>4.846386432647705</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8937,7 +8937,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D524">
-        <v>9.572282791137695</v>
+        <v>12.87405967712402</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8951,7 +8951,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D525">
-        <v>-8.19686222076416</v>
+        <v>-4.879226207733154</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8965,7 +8965,7 @@
         <v>-16.79999923706055</v>
       </c>
       <c r="D526">
-        <v>-15.70168399810791</v>
+        <v>-13.54083251953125</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8979,7 +8979,7 @@
         <v>4</v>
       </c>
       <c r="D527">
-        <v>2.097668886184692</v>
+        <v>1.774046421051025</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8993,7 +8993,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D528">
-        <v>-1.174706697463989</v>
+        <v>-4.69380521774292</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9007,7 +9007,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D529">
-        <v>1.773561120033264</v>
+        <v>0.9713382124900818</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9021,7 +9021,7 @@
         <v>-33.29999923706055</v>
       </c>
       <c r="D530">
-        <v>-23.16158294677734</v>
+        <v>-19.28298377990723</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9035,7 +9035,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D531">
-        <v>4.819314479827881</v>
+        <v>4.699417591094971</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9049,7 +9049,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D532">
-        <v>-0.07228974997997284</v>
+        <v>-3.121997356414795</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9063,7 +9063,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D533">
-        <v>-12.67919540405273</v>
+        <v>-11.98036956787109</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9077,7 +9077,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D534">
-        <v>15.96181583404541</v>
+        <v>15.59248352050781</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9091,7 +9091,7 @@
         <v>-13.89999961853027</v>
       </c>
       <c r="D535">
-        <v>-8.008981704711914</v>
+        <v>-10.16453838348389</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9105,7 +9105,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D536">
-        <v>-2.716177225112915</v>
+        <v>-1.862399816513062</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9119,7 +9119,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D537">
-        <v>-2.394952058792114</v>
+        <v>-1.978594064712524</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9133,7 +9133,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D538">
-        <v>2.993703126907349</v>
+        <v>5.42841100692749</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9147,7 +9147,7 @@
         <v>-11.5</v>
       </c>
       <c r="D539">
-        <v>-10.88929080963135</v>
+        <v>-9.057754516601562</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9161,7 +9161,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D540">
-        <v>4.439810752868652</v>
+        <v>3.53380298614502</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9175,7 +9175,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D541">
-        <v>1.118730306625366</v>
+        <v>1.20405125617981</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9189,7 +9189,7 @@
         <v>-55.20000076293945</v>
       </c>
       <c r="D542">
-        <v>-45.00877380371094</v>
+        <v>-36.25875091552734</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9203,7 +9203,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D543">
-        <v>-13.17184829711914</v>
+        <v>-9.726850509643555</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9217,7 +9217,7 @@
         <v>8</v>
       </c>
       <c r="D544">
-        <v>2.815513849258423</v>
+        <v>2.106249332427979</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9231,7 +9231,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D545">
-        <v>-8.041029930114746</v>
+        <v>-9.846514701843262</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9245,7 +9245,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D546">
-        <v>2.07438063621521</v>
+        <v>3.904934406280518</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9259,7 +9259,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D547">
-        <v>-2.942981004714966</v>
+        <v>-3.083798408508301</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9273,7 +9273,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D548">
-        <v>4.054195404052734</v>
+        <v>6.964440822601318</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9287,7 +9287,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D549">
-        <v>-2.852841854095459</v>
+        <v>-1.930272102355957</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9301,7 +9301,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D550">
-        <v>-8.537687301635742</v>
+        <v>-8.80112361907959</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9315,7 +9315,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D551">
-        <v>-3.450231552124023</v>
+        <v>-1.156141877174377</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9329,7 +9329,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>4.724179267883301</v>
+        <v>4.555352210998535</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9343,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="D553">
-        <v>0.3852623105049133</v>
+        <v>-0.09990519285202026</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9357,7 +9357,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D554">
-        <v>-0.01935987174510956</v>
+        <v>0.2750660181045532</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9371,7 +9371,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D555">
-        <v>1.006723642349243</v>
+        <v>1.34719181060791</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9385,7 +9385,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D556">
-        <v>-0.06588293612003326</v>
+        <v>-1.811462163925171</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9399,7 +9399,7 @@
         <v>5.5</v>
       </c>
       <c r="D557">
-        <v>1.786385059356689</v>
+        <v>1.29244589805603</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9413,7 +9413,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D558">
-        <v>3.41458797454834</v>
+        <v>3.039309024810791</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9427,7 +9427,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D559">
-        <v>0.7359665036201477</v>
+        <v>0.4101391434669495</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9441,7 +9441,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D560">
-        <v>4.467625141143799</v>
+        <v>2.050604343414307</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9455,7 +9455,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D561">
-        <v>-0.6275055408477783</v>
+        <v>-1.063353300094604</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9469,7 +9469,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D562">
-        <v>2.926418542861938</v>
+        <v>2.397045612335205</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9483,7 +9483,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D563">
-        <v>-0.1692364364862442</v>
+        <v>-0.5433886051177979</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9497,7 +9497,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D564">
-        <v>3.608139514923096</v>
+        <v>4.593239784240723</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9511,7 +9511,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D565">
-        <v>-0.40181964635849</v>
+        <v>9.702375411987305</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9525,7 +9525,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D566">
-        <v>2.556170701980591</v>
+        <v>2.555123805999756</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9539,7 +9539,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D567">
-        <v>11.35882472991943</v>
+        <v>10.27927684783936</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9553,7 +9553,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D568">
-        <v>-1.397958040237427</v>
+        <v>-3.058995008468628</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9567,7 +9567,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D569">
-        <v>1.592041730880737</v>
+        <v>0.856723964214325</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9581,7 +9581,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D570">
-        <v>12.23675537109375</v>
+        <v>14.35433959960938</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9595,7 +9595,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D571">
-        <v>1.24430251121521</v>
+        <v>0.2752373814582825</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9609,7 +9609,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D572">
-        <v>-0.48274827003479</v>
+        <v>0.5371035933494568</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="D573">
-        <v>0.5846809148788452</v>
+        <v>0.01649123430252075</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9637,7 +9637,7 @@
         <v>-1.5</v>
       </c>
       <c r="D574">
-        <v>0.5409173965454102</v>
+        <v>-0.4455225467681885</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9651,7 +9651,7 @@
         <v>3.5</v>
       </c>
       <c r="D575">
-        <v>2.676835298538208</v>
+        <v>1.417951583862305</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9665,7 +9665,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D576">
-        <v>-1.293238282203674</v>
+        <v>-1.113952398300171</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9679,7 +9679,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D577">
-        <v>-8.099865913391113</v>
+        <v>-7.988461494445801</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9693,7 +9693,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D578">
-        <v>-8.397137641906738</v>
+        <v>-9.339334487915039</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9707,7 +9707,7 @@
         <v>-23.39999961853027</v>
       </c>
       <c r="D579">
-        <v>-14.98823356628418</v>
+        <v>-15.18526363372803</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9721,7 +9721,7 @@
         <v>-10</v>
       </c>
       <c r="D580">
-        <v>-7.487191200256348</v>
+        <v>-6.108973979949951</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9735,7 +9735,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D581">
-        <v>-4.727695465087891</v>
+        <v>-3.992834091186523</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9749,7 +9749,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D582">
-        <v>1.78727662563324</v>
+        <v>1.462020874023438</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9763,7 +9763,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D583">
-        <v>-18.81353187561035</v>
+        <v>-18.0664119720459</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9777,7 +9777,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D584">
-        <v>1.031488537788391</v>
+        <v>2.669541597366333</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9791,7 +9791,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D585">
-        <v>7.333178997039795</v>
+        <v>6.119631767272949</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9805,7 +9805,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D586">
-        <v>11.27991580963135</v>
+        <v>11.00026702880859</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="D587">
-        <v>-1.74526309967041</v>
+        <v>-1.245387315750122</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9833,7 +9833,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D588">
-        <v>1.949655294418335</v>
+        <v>2.08753490447998</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9847,7 +9847,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D589">
-        <v>-6.848426818847656</v>
+        <v>-3.102182626724243</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9861,7 +9861,7 @@
         <v>-1</v>
       </c>
       <c r="D590">
-        <v>-3.354077577590942</v>
+        <v>-2.015486001968384</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9875,7 +9875,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D591">
-        <v>-6.789333343505859</v>
+        <v>-0.9772642254829407</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9889,7 +9889,7 @@
         <v>-21.10000038146973</v>
       </c>
       <c r="D592">
-        <v>-29.2325439453125</v>
+        <v>-24.04152488708496</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9903,7 +9903,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D593">
-        <v>1.965828418731689</v>
+        <v>1.485924959182739</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9917,7 +9917,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D594">
-        <v>2.547213554382324</v>
+        <v>2.417258739471436</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9931,7 +9931,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D595">
-        <v>-0.3775673508644104</v>
+        <v>0.8044537901878357</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9945,7 +9945,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D596">
-        <v>1.736080169677734</v>
+        <v>0.4506449103355408</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9959,7 +9959,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D597">
-        <v>-9.380017280578613</v>
+        <v>-6.956119060516357</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9973,7 +9973,7 @@
         <v>-2</v>
       </c>
       <c r="D598">
-        <v>0.08079464733600616</v>
+        <v>0.2252932190895081</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9987,7 +9987,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D599">
-        <v>0.6317012906074524</v>
+        <v>0.7085044980049133</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10001,7 +10001,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D600">
-        <v>-4.142378807067871</v>
+        <v>-3.961380958557129</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10015,7 +10015,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D601">
-        <v>1.064093708992004</v>
+        <v>0.8490980267524719</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10029,7 +10029,7 @@
         <v>-18.39999961853027</v>
       </c>
       <c r="D602">
-        <v>-12.93535232543945</v>
+        <v>-10.23780536651611</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10043,7 +10043,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D603">
-        <v>3.765051126480103</v>
+        <v>2.520636081695557</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10057,7 +10057,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D604">
-        <v>-1.367921233177185</v>
+        <v>-2.003036260604858</v>
       </c>
     </row>
   </sheetData>
